--- a/artfynd/A 46964-2020 artfynd.xlsx
+++ b/artfynd/A 46964-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46964-2020 artfynd.xlsx
+++ b/artfynd/A 46964-2020 artfynd.xlsx
@@ -1847,7 +1847,7 @@
         <v>100362672</v>
       </c>
       <c r="B12" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>573722.9331366664</v>
+        <v>573723</v>
       </c>
       <c r="R12" t="n">
-        <v>6907435.204697234</v>
+        <v>6907435</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1922,19 +1922,9 @@
           <t>2021-09-13</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-09-13</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 46964-2020 artfynd.xlsx
+++ b/artfynd/A 46964-2020 artfynd.xlsx
@@ -1847,7 +1847,7 @@
         <v>100362672</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 46964-2020 artfynd.xlsx
+++ b/artfynd/A 46964-2020 artfynd.xlsx
@@ -1847,7 +1847,7 @@
         <v>100362672</v>
       </c>
       <c r="B12" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 46964-2020 artfynd.xlsx
+++ b/artfynd/A 46964-2020 artfynd.xlsx
@@ -1847,7 +1847,7 @@
         <v>100362672</v>
       </c>
       <c r="B12" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
